--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -505,7 +505,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour gérer le code région définissant la région source des données</t>
@@ -3644,15 +3644,15 @@
   <dimension ref="A1:AM289"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="91.7109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.28125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="45.6484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="78.625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.25" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="39.1328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3663,25 +3663,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="81.27734375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="131.5625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="69.6796875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="112.7890625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="59.33203125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="58.1796875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="63.42578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="63.578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="49.87890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="54.375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="54.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4463,7 +4463,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>249</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>255</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>289</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>295</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>301</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>307</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>313</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>319</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>325</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>331</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>337</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>343</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>349</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>352</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>357</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>363</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>369</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>431</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>438</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>445</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>452</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>459</v>
       </c>
@@ -13890,7 +13890,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>466</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>473</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>481</v>
       </c>
@@ -15454,7 +15454,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>488</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>494</v>
       </c>
@@ -16459,7 +16459,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>501</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>508</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>515</v>
       </c>
@@ -17910,7 +17910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
         <v>520</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>635</v>
       </c>
@@ -22840,7 +22840,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>640</v>
       </c>
@@ -22953,7 +22953,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>644</v>
       </c>
@@ -23066,7 +23066,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
         <v>649</v>
       </c>
@@ -23179,7 +23179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
         <v>654</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
         <v>659</v>
       </c>
@@ -23845,7 +23845,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="182" hidden="true">
+    <row r="182">
       <c r="A182" t="s" s="2">
         <v>680</v>
       </c>
@@ -23958,7 +23958,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
         <v>686</v>
       </c>
@@ -24402,7 +24402,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
         <v>701</v>
       </c>
@@ -24513,7 +24513,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="188" hidden="true">
+    <row r="188">
       <c r="A188" t="s" s="2">
         <v>706</v>
       </c>
@@ -24624,7 +24624,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="189" hidden="true">
+    <row r="189">
       <c r="A189" t="s" s="2">
         <v>711</v>
       </c>
@@ -24846,7 +24846,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
         <v>723</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" hidden="true">
+    <row r="195">
       <c r="A195" t="s" s="2">
         <v>748</v>
       </c>
@@ -26174,7 +26174,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
         <v>772</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="216" hidden="true">
+    <row r="216">
       <c r="A216" t="s" s="2">
         <v>802</v>
       </c>
@@ -28604,7 +28604,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="225" hidden="true">
+    <row r="225">
       <c r="A225" t="s" s="2">
         <v>841</v>
       </c>
@@ -28715,7 +28715,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="226" hidden="true">
+    <row r="226">
       <c r="A226" t="s" s="2">
         <v>847</v>
       </c>
@@ -28826,7 +28826,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="227" hidden="true">
+    <row r="227">
       <c r="A227" t="s" s="2">
         <v>853</v>
       </c>
@@ -28937,7 +28937,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="228" hidden="true">
+    <row r="228">
       <c r="A228" t="s" s="2">
         <v>859</v>
       </c>
@@ -29486,7 +29486,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="233" hidden="true">
+    <row r="233">
       <c r="A233" t="s" s="2">
         <v>874</v>
       </c>
@@ -30033,7 +30033,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="238" hidden="true">
+    <row r="238">
       <c r="A238" t="s" s="2">
         <v>886</v>
       </c>
@@ -30582,7 +30582,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="243" hidden="true">
+    <row r="243">
       <c r="A243" t="s" s="2">
         <v>897</v>
       </c>
@@ -31131,7 +31131,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" hidden="true">
+    <row r="248">
       <c r="A248" t="s" s="2">
         <v>908</v>
       </c>
@@ -31789,7 +31789,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="254" hidden="true">
+    <row r="254">
       <c r="A254" t="s" s="2">
         <v>919</v>
       </c>
@@ -32122,7 +32122,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="257" hidden="true">
+    <row r="257">
       <c r="A257" t="s" s="2">
         <v>938</v>
       </c>
@@ -32457,7 +32457,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="260" hidden="true">
+    <row r="260">
       <c r="A260" t="s" s="2">
         <v>956</v>
       </c>
@@ -33565,7 +33565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="270" hidden="true">
+    <row r="270">
       <c r="A270" t="s" s="2">
         <v>995</v>
       </c>
@@ -33676,7 +33676,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="271" hidden="true">
+    <row r="271">
       <c r="A271" t="s" s="2">
         <v>1000</v>
       </c>
@@ -33787,7 +33787,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="272" hidden="true">
+    <row r="272">
       <c r="A272" t="s" s="2">
         <v>1005</v>
       </c>
@@ -34011,7 +34011,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="274" hidden="true">
+    <row r="274">
       <c r="A274" t="s" s="2">
         <v>1015</v>
       </c>
@@ -34122,7 +34122,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="275" hidden="true">
+    <row r="275">
       <c r="A275" t="s" s="2">
         <v>1022</v>
       </c>
@@ -34677,7 +34677,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="280" hidden="true">
+    <row r="280">
       <c r="A280" t="s" s="2">
         <v>1037</v>
       </c>
@@ -34788,7 +34788,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="281" hidden="true">
+    <row r="281">
       <c r="A281" t="s" s="2">
         <v>1038</v>
       </c>
@@ -34899,7 +34899,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="282" hidden="true">
+    <row r="282">
       <c r="A282" t="s" s="2">
         <v>1039</v>
       </c>
@@ -35121,7 +35121,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="284" hidden="true">
+    <row r="284">
       <c r="A284" t="s" s="2">
         <v>1042</v>
       </c>
@@ -35797,12 +35797,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM289">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-organization.xlsx
+++ b/main/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
